--- a/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_osh_normal_00001/vd_osh_normal_00001_design.xlsx
+++ b/domain/tasks/20260310_115400_vd_ingame_masterdata_generation/vd-ingame-creator/vd_osh_normal_00001/vd_osh_normal_00001_design.xlsx
@@ -333,14 +333,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -668,7 +668,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t>ブロック基礎設計_vd_osh_normal_00001</t>
         </is>
@@ -718,21 +718,21 @@
     </row>
     <row r="4" ht="186" customHeight="1">
       <c r="A4" s="6" t="n"/>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="27" t="inlineStr">
         <is>
           <t>【推しの子】の世界観を反映したノーマルブロックです。ステージに登場するのは、B小町メンバーである星野ルビー・MEMちょ・有馬かな・黒川あかねの4名のプレイアブルキャラ（c_キャラ）と、共通敵のファントムです。
 難易度設計としては、開幕にファントムを複数体出現させてプレイヤーの初動を促し、その後c_キャラが撃破トリガーや時間トリガーで1体ずつ登場する構成をとっています。c_キャラはプレイヤーキャラが敵として出現するため、世界観上同一キャラが複数体同時にフィールドに存在する状況を避け、それぞれ個別召喚で対処します。
 合計7行のシーケンス構成で、ファントム3波＋c_キャラ4種が各1体ずつ（FriendUnitDead累積カウントによる再出撃あり）登場し、最低15体以上の出現を保証しています。バトルのテンポは序盤に速く、中盤以降は手ごわいc_キャラが登場して緊張感を高める体験を目指しています。</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="28" t="n"/>
+      <c r="C4" s="28" t="n"/>
+      <c r="D4" s="28" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="28" t="n"/>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="28" t="n"/>
+      <c r="J4" s="29" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="L4" s="6" t="n"/>
       <c r="M4" s="6" t="n"/>
@@ -835,35 +835,35 @@
     </row>
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="2" t="n"/>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>vd_osh_normal_00001</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="E9" s="29" t="inlineStr">
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>3行</t>
         </is>
       </c>
-      <c r="F9" s="29" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>なし（デフォルトグループのみ）</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>7行</t>
         </is>
       </c>
-      <c r="H9" s="29" t="n">
+      <c r="H9" s="27" t="n">
         <v>202604010</v>
       </c>
       <c r="I9" s="2" t="n"/>
@@ -962,23 +962,23 @@
     </row>
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="2" t="n"/>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>行1</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>3コマ</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr"/>
-      <c r="E14" s="29" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr"/>
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>0.25 / 0.50 / 0.25</t>
         </is>
@@ -993,23 +993,23 @@
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="2" t="n"/>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>行2</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>2コマ</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr"/>
-      <c r="E15" s="29" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr"/>
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>0.50 / 0.50</t>
         </is>
@@ -1024,23 +1024,23 @@
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="2" t="n"/>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>行3</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>3コマ</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr"/>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr"/>
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>0.40 / 0.20 / 0.40</t>
         </is>
@@ -1238,22 +1238,22 @@
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="2" t="n"/>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>c_osh_00201_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>星野 ルビー</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>Green（緑属性）</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
+      <c r="E26" s="27" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
@@ -1261,13 +1261,13 @@
       <c r="F26" s="30" t="n">
         <v>50000</v>
       </c>
-      <c r="G26" s="29" t="n">
+      <c r="G26" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="H26" s="29" t="n">
+      <c r="H26" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="I26" s="29" t="inlineStr">
+      <c r="I26" s="27" t="inlineStr">
         <is>
           <t>雑魚（c_キャラ）</t>
         </is>
@@ -1279,22 +1279,22 @@
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="2" t="n"/>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>c_osh_00301_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="C27" s="29" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
         <is>
           <t>MEMちょ</t>
         </is>
       </c>
-      <c r="D27" s="29" t="inlineStr">
+      <c r="D27" s="27" t="inlineStr">
         <is>
           <t>Green（緑属性）</t>
         </is>
       </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>Support</t>
         </is>
@@ -1302,13 +1302,13 @@
       <c r="F27" s="30" t="n">
         <v>50000</v>
       </c>
-      <c r="G27" s="29" t="n">
+      <c r="G27" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="H27" s="29" t="n">
+      <c r="H27" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="I27" s="29" t="inlineStr">
+      <c r="I27" s="27" t="inlineStr">
         <is>
           <t>雑魚（c_キャラ）</t>
         </is>
@@ -1318,24 +1318,24 @@
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="13" customHeight="1">
       <c r="A28" s="2" t="n"/>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>c_osh_00401_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>有馬 かな</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>Green（緑属性）</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
+      <c r="E28" s="27" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
@@ -1343,13 +1343,13 @@
       <c r="F28" s="30" t="n">
         <v>50000</v>
       </c>
-      <c r="G28" s="29" t="n">
+      <c r="G28" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="H28" s="29" t="n">
+      <c r="H28" s="27" t="n">
         <v>32</v>
       </c>
-      <c r="I28" s="29" t="inlineStr">
+      <c r="I28" s="27" t="inlineStr">
         <is>
           <t>雑魚（c_キャラ）</t>
         </is>
@@ -1359,24 +1359,24 @@
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
     </row>
-    <row r="29" ht="24" customHeight="1">
+    <row r="29" ht="13" customHeight="1">
       <c r="A29" s="2" t="n"/>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>c_osh_00501_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" s="27" t="inlineStr">
         <is>
           <t>黒川 あかね</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="27" t="inlineStr">
         <is>
           <t>Green（緑属性）</t>
         </is>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E29" s="27" t="inlineStr">
         <is>
           <t>Technical</t>
         </is>
@@ -1384,13 +1384,13 @@
       <c r="F29" s="30" t="n">
         <v>10000</v>
       </c>
-      <c r="G29" s="29" t="n">
+      <c r="G29" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="H29" s="29" t="n">
+      <c r="H29" s="27" t="n">
         <v>30</v>
       </c>
-      <c r="I29" s="29" t="inlineStr">
+      <c r="I29" s="27" t="inlineStr">
         <is>
           <t>雑魚（c_キャラ）</t>
         </is>
@@ -1400,24 +1400,24 @@
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
     </row>
-    <row r="30" ht="24" customHeight="1">
+    <row r="30" ht="13" customHeight="1">
       <c r="A30" s="2" t="n"/>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>ファントム</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>Colorless（無属性）</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
+      <c r="E30" s="27" t="inlineStr">
         <is>
           <t>Attack</t>
         </is>
@@ -1425,13 +1425,13 @@
       <c r="F30" s="30" t="n">
         <v>5000</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G30" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="H30" s="29" t="n">
+      <c r="H30" s="27" t="n">
         <v>34</v>
       </c>
-      <c r="I30" s="29" t="inlineStr">
+      <c r="I30" s="27" t="inlineStr">
         <is>
           <t>雑魚（共通）</t>
         </is>
@@ -1610,31 +1610,31 @@
     </row>
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="2" t="n"/>
-      <c r="B40" s="29" t="n">
+      <c r="B40" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="E40" s="29" t="inlineStr">
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
-      <c r="F40" s="29" t="inlineStr">
+      <c r="F40" s="27" t="inlineStr">
         <is>
           <t>ファントム</t>
         </is>
       </c>
-      <c r="G40" s="29" t="n">
+      <c r="G40" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H40" s="29" t="inlineStr">
+      <c r="H40" s="27" t="inlineStr">
         <is>
           <t>開幕5体・序盤の圧力</t>
         </is>
@@ -1647,31 +1647,31 @@
     </row>
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="2" t="n"/>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" s="27" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="E41" s="29" t="inlineStr">
+      <c r="E41" s="27" t="inlineStr">
         <is>
           <t>c_osh_00201_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="F41" s="29" t="inlineStr">
+      <c r="F41" s="27" t="inlineStr">
         <is>
           <t>星野 ルビー</t>
         </is>
       </c>
-      <c r="G41" s="29" t="n">
+      <c r="G41" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="29" t="inlineStr">
+      <c r="H41" s="27" t="inlineStr">
         <is>
           <t>初のc_キャラ登場</t>
         </is>
@@ -1684,10 +1684,10 @@
     </row>
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="2" t="n"/>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="C42" s="29" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>FriendUnitDead</t>
         </is>
@@ -1695,20 +1695,20 @@
       <c r="D42" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="29" t="inlineStr">
+      <c r="E42" s="27" t="inlineStr">
         <is>
           <t>c_osh_00301_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="F42" s="29" t="inlineStr">
+      <c r="F42" s="27" t="inlineStr">
         <is>
           <t>MEMちょ</t>
         </is>
       </c>
-      <c r="G42" s="29" t="n">
+      <c r="G42" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="29" t="inlineStr">
+      <c r="H42" s="27" t="inlineStr">
         <is>
           <t>累計1体撃破で登場</t>
         </is>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="2" t="n"/>
-      <c r="B43" s="29" t="n">
+      <c r="B43" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="C43" s="29" t="inlineStr">
+      <c r="C43" s="27" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
@@ -1732,20 +1732,20 @@
       <c r="D43" s="30" t="n">
         <v>3000</v>
       </c>
-      <c r="E43" s="29" t="inlineStr">
+      <c r="E43" s="27" t="inlineStr">
         <is>
           <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
-      <c r="F43" s="29" t="inlineStr">
+      <c r="F43" s="27" t="inlineStr">
         <is>
           <t>ファントム</t>
         </is>
       </c>
-      <c r="G43" s="29" t="n">
+      <c r="G43" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H43" s="29" t="inlineStr">
+      <c r="H43" s="27" t="inlineStr">
         <is>
           <t>中盤ファントム増援</t>
         </is>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="2" t="n"/>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>FriendUnitDead</t>
         </is>
@@ -1769,20 +1769,20 @@
       <c r="D44" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="E44" s="29" t="inlineStr">
+      <c r="E44" s="27" t="inlineStr">
         <is>
           <t>c_osh_00401_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="F44" s="29" t="inlineStr">
+      <c r="F44" s="27" t="inlineStr">
         <is>
           <t>有馬 かな</t>
         </is>
       </c>
-      <c r="G44" s="29" t="n">
+      <c r="G44" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H44" s="29" t="inlineStr">
+      <c r="H44" s="27" t="inlineStr">
         <is>
           <t>累計3体撃破で登場</t>
         </is>
@@ -1793,33 +1793,33 @@
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
     </row>
-    <row r="45" ht="24" customHeight="1">
+    <row r="45" ht="13" customHeight="1">
       <c r="A45" s="2" t="n"/>
-      <c r="B45" s="29" t="n">
+      <c r="B45" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="C45" s="27" t="inlineStr">
         <is>
           <t>FriendUnitDead</t>
         </is>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E45" s="29" t="inlineStr">
+      <c r="E45" s="27" t="inlineStr">
         <is>
           <t>c_osh_00501_vd_Normal_Green</t>
         </is>
       </c>
-      <c r="F45" s="29" t="inlineStr">
+      <c r="F45" s="27" t="inlineStr">
         <is>
           <t>黒川 あかね</t>
         </is>
       </c>
-      <c r="G45" s="29" t="n">
+      <c r="G45" s="27" t="n">
         <v>1</v>
       </c>
-      <c r="H45" s="29" t="inlineStr">
+      <c r="H45" s="27" t="inlineStr">
         <is>
           <t>累計5体撃破で登場</t>
         </is>
@@ -1830,33 +1830,33 @@
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
     </row>
-    <row r="46" ht="24" customHeight="1">
+    <row r="46" ht="13" customHeight="1">
       <c r="A46" s="2" t="n"/>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="C46" s="29" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>ElapsedTime</t>
         </is>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="27" t="n">
         <v>5000</v>
       </c>
-      <c r="E46" s="29" t="inlineStr">
+      <c r="E46" s="27" t="inlineStr">
         <is>
           <t>e_glo_00001_vd_Normal_Colorless</t>
         </is>
       </c>
-      <c r="F46" s="29" t="inlineStr">
+      <c r="F46" s="27" t="inlineStr">
         <is>
           <t>ファントム</t>
         </is>
       </c>
-      <c r="G46" s="29" t="n">
+      <c r="G46" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="29" t="inlineStr">
+      <c r="H46" s="27" t="inlineStr">
         <is>
           <t>終盤ファントム最終波</t>
         </is>
@@ -2033,10 +2033,10 @@
           <t>内容</t>
         </is>
       </c>
-      <c r="D57" s="27" t="n"/>
-      <c r="E57" s="27" t="n"/>
-      <c r="F57" s="27" t="n"/>
-      <c r="G57" s="28" t="n"/>
+      <c r="D57" s="28" t="n"/>
+      <c r="E57" s="28" t="n"/>
+      <c r="F57" s="28" t="n"/>
+      <c r="G57" s="29" t="n"/>
       <c r="H57" s="16" t="n"/>
       <c r="I57" s="16" t="n"/>
       <c r="J57" s="16" t="n"/>
@@ -2052,10 +2052,10 @@
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr"/>
-      <c r="D58" s="27" t="n"/>
-      <c r="E58" s="27" t="n"/>
-      <c r="F58" s="27" t="n"/>
-      <c r="G58" s="28" t="n"/>
+      <c r="D58" s="28" t="n"/>
+      <c r="E58" s="28" t="n"/>
+      <c r="F58" s="28" t="n"/>
+      <c r="G58" s="29" t="n"/>
       <c r="H58" s="16" t="n"/>
       <c r="I58" s="16" t="n"/>
       <c r="J58" s="16" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="C59" s="18" t="inlineStr"/>
-      <c r="D59" s="27" t="n"/>
-      <c r="E59" s="27" t="n"/>
-      <c r="F59" s="27" t="n"/>
-      <c r="G59" s="28" t="n"/>
+      <c r="D59" s="28" t="n"/>
+      <c r="E59" s="28" t="n"/>
+      <c r="F59" s="28" t="n"/>
+      <c r="G59" s="29" t="n"/>
       <c r="H59" s="16" t="n"/>
       <c r="I59" s="16" t="n"/>
       <c r="J59" s="16" t="n"/>
